--- a/Templates/Documentation_Template.xlsx
+++ b/Templates/Documentation_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E91CDB-B160-4FC6-97F9-267768D0FB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27240FBD-1BFE-4895-87F7-DF323AA4F561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DB1217F5-3EDD-4456-A020-305ADC7C8E64}"/>
   </bookViews>
@@ -142,9 +142,6 @@
     <t>[scenario name]</t>
   </si>
   <si>
-    <t xml:space="preserve">[write a description of the scenario including </t>
-  </si>
-  <si>
     <t>kg/[declared unit]</t>
   </si>
   <si>
@@ -163,6 +160,9 @@
     <t>EcoInvent database version: [EcoInvent version]
 Impact assessment method: ReCiPe2016 Midpoint (H)
 [other relevant comments like references, description of mass factor etc.]</t>
+  </si>
+  <si>
+    <t>[write a description of the scenario including key assumptions]</t>
   </si>
 </sst>
 </file>
@@ -482,38 +482,14 @@
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -523,24 +499,48 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -952,7 +952,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -972,10 +972,10 @@
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="36"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -1002,15 +1002,15 @@
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="91.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="26"/>
+      <c r="A11" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
@@ -1036,12 +1036,12 @@
       <c r="A14" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="F14" s="9" t="s">
         <v>8</v>
       </c>
@@ -1050,54 +1050,54 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="43" t="s">
+      <c r="A15" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
+      <c r="B15" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
       <c r="F15" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="22" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="44" t="s">
+      <c r="G16" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="22" t="s">
+      <c r="B17" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="23" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="23" t="s">
-        <v>27</v>
-      </c>
       <c r="G17" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1130,18 +1130,18 @@
       <c r="C20" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37" t="s">
+      <c r="E20" s="29"/>
+      <c r="F20" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="38"/>
+      <c r="G20" s="30"/>
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
-        <v>29</v>
+      <c r="A21" s="24" t="s">
+        <v>28</v>
       </c>
       <c r="B21" s="15">
         <v>0</v>
@@ -1149,18 +1149,18 @@
       <c r="C21" s="15">
         <v>0</v>
       </c>
-      <c r="D21" s="29">
-        <v>0</v>
-      </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29">
-        <v>0</v>
-      </c>
-      <c r="G21" s="30"/>
+      <c r="D21" s="31">
+        <v>0</v>
+      </c>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31">
+        <v>0</v>
+      </c>
+      <c r="G21" s="42"/>
     </row>
     <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="41" t="s">
-        <v>29</v>
+      <c r="A22" s="25" t="s">
+        <v>28</v>
       </c>
       <c r="B22" s="14">
         <v>0</v>
@@ -1168,18 +1168,18 @@
       <c r="C22" s="14">
         <v>0</v>
       </c>
-      <c r="D22" s="31">
-        <v>0</v>
-      </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31">
-        <v>0</v>
-      </c>
-      <c r="G22" s="32"/>
+      <c r="D22" s="32">
+        <v>0</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32">
+        <v>0</v>
+      </c>
+      <c r="G22" s="43"/>
     </row>
     <row r="23" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
-        <v>29</v>
+      <c r="A23" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="B23" s="16">
         <v>0</v>
@@ -1187,14 +1187,14 @@
       <c r="C23" s="16">
         <v>0</v>
       </c>
-      <c r="D23" s="27">
-        <v>0</v>
-      </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27">
-        <v>0</v>
-      </c>
-      <c r="G23" s="33"/>
+      <c r="D23" s="40">
+        <v>0</v>
+      </c>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40">
+        <v>0</v>
+      </c>
+      <c r="G23" s="44"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
@@ -1206,14 +1206,14 @@
       <c r="C24" s="17">
         <v>0</v>
       </c>
-      <c r="D24" s="28">
-        <v>0</v>
-      </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28">
-        <v>0</v>
-      </c>
-      <c r="G24" s="34"/>
+      <c r="D24" s="41">
+        <v>0</v>
+      </c>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41">
+        <v>0</v>
+      </c>
+      <c r="G24" s="45"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
@@ -1236,18 +1236,25 @@
       <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:7" ht="114.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="26"/>
+      <c r="A27" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="F20:G20"/>
@@ -1258,13 +1265,6 @@
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
